--- a/invoices/exports/expenses-2026-05-06.xlsx
+++ b/invoices/exports/expenses-2026-05-06.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +37,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -62,13 +68,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,15 +443,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:H247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,15 +474,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>סכום</t>
+          <t>מטבע</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>מטבע</t>
+          <t>סכום מקורי</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>שער המרה</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>סכום בש"ח</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
@@ -493,15 +514,21 @@
           <t>69f4787e321e7b5dd037f7b8</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,15 +546,21 @@
           <t>69f487369e71c66ea91b36c5</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>155.93</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>155.93</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -545,15 +578,21 @@
           <t>69f4b1085f9d3dfb80282064</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,15 +610,21 @@
           <t>69f635d7bf445b3b7a666ade</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>268.9</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>268.9</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -597,15 +642,21 @@
           <t>69f6395e571bb252d050912e</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -623,15 +674,21 @@
           <t>69f62dc0904fde7518d3a5c5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>201.2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>201.2</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -649,15 +706,21 @@
           <t>770129016663</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -675,15 +738,21 @@
           <t>69f718f36db9190ea5d7173f</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -701,15 +770,21 @@
           <t>66948</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>78.36</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>טעינת רכב חשמלי</t>
         </is>
@@ -731,15 +806,21 @@
           <t>34939</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>559</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>כיבוד</t>
         </is>
@@ -761,15 +842,21 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>נסיעה עבור דבורה</t>
         </is>
@@ -791,15 +878,21 @@
           <t>69f86ac303c1284ed4ebb775</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>57.25</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -817,15 +910,21 @@
           <t>69f889daf45c5f844f4694f2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -843,15 +942,21 @@
           <t>69f8d650a25d92c21a043f7e</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>137.6</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>137.6</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -869,15 +974,21 @@
           <t>69f84267bdce63c9bb52d26e</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>134.3</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -895,15 +1006,21 @@
           <t>69f8d9e9a486ba8e34de785b</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>128.35</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>128.35</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -921,15 +1038,21 @@
           <t>12316</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>עבור רפאל ארי דן-גור</t>
         </is>
@@ -951,15 +1074,21 @@
           <t>694129594835</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>135.6</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -977,15 +1106,21 @@
           <t>0218-8897</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>317.42</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>317.42</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>מנוי חודשי מאי</t>
         </is>
@@ -1007,15 +1142,21 @@
           <t>69fb16e981a6a64ec144b277</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1033,15 +1174,21 @@
           <t>69fb1437731001c8253ba5c9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1059,15 +1206,21 @@
           <t>69fb255624e0613b4049704d</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1085,15 +1238,21 @@
           <t>69fb4d5b62f2057f455da7c3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>332.9</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>332.9</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1111,15 +1270,21 @@
           <t>69fae5fc025578e2b945cc29</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
         <v>200.88</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>200.88</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1137,15 +1302,21 @@
           <t>1214</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>900</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>אפיון מערכת לאדוונס אסתטיק</t>
         </is>
@@ -1167,15 +1338,21 @@
           <t>01/010053</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>6490</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>6490</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>שכירות 05/26 לאדוונס אסתטיק - שיק</t>
         </is>
@@ -1197,15 +1374,21 @@
           <t>69fcd1e4911fc27586811922</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>119.45</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1223,15 +1406,21 @@
           <t>69fc889c3063627a0ae5a7a1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1249,15 +1438,21 @@
           <t>69fccfd04fedff9d51da4333</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1275,15 +1470,21 @@
           <t>69fc54c2f360c05a57d4b2ba</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
         <v>427.9</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>427.9</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1301,15 +1502,21 @@
           <t>2895-4962-2216</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" s="4" t="n">
+        <v>2.9051</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1327,15 +1534,21 @@
           <t>69fd69acf799cbb19063de41</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
         <v>493.9</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1353,15 +1566,21 @@
           <t>6a00c9d75c75ed876f8ffa4d</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
         <v>171.9</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>171.9</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1379,15 +1598,21 @@
           <t>6a001a6d68f9dd6fc69f9289</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
         <v>29.25</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1405,15 +1630,21 @@
           <t>6a001cc0dabb1d91c7612051</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1431,15 +1662,21 @@
           <t>6a003f4dc56433f7e45cd75f</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1457,15 +1694,21 @@
           <t>61604</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1483,15 +1726,21 @@
           <t>6a02145875a7de0f8bb360f7</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
         <v>214.9</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>214.9</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1509,15 +1758,21 @@
           <t>6a01a318949e73033fc589cc</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1535,15 +1790,21 @@
           <t>6a01ddec76b3633768f80616</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
         <v>88.2</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1561,15 +1822,21 @@
           <t>6a019b9aca5abcb4a8c24f0a</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
         <v>333.9</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>333.9</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1587,15 +1854,21 @@
           <t>6a02156801ddd64929ba8b3c</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1613,15 +1886,21 @@
           <t>6a02dcb97bcdec6ef6c0c832</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1639,15 +1918,21 @@
           <t>6a0312f7177030f53ba8c3e6</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1665,15 +1950,21 @@
           <t>2725-0862-6445</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" s="4" t="n">
+        <v>2.9079</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1691,15 +1982,21 @@
           <t>734132968875</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1717,15 +2014,21 @@
           <t>6a04ae5acfec708fea12d230</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
         <v>199.9</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1743,15 +2046,21 @@
           <t>6a0488413be1c9c9dc5ba7d4</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
         <v>318.94</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>318.94</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1769,15 +2078,21 @@
           <t>2928-7612-1710</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" s="4" t="n">
+        <v>2.9053</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>130.74</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1795,15 +2110,21 @@
           <t>6a05693820326f9388f24905</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
         <v>636.9</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>636.9</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1821,15 +2142,21 @@
           <t>6a05ac2fc70738ad574d9785</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
         <v>25.05</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1847,15 +2174,21 @@
           <t>6a05b6ed40e77674933b837b</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1873,15 +2206,21 @@
           <t>6a05d390d96692d2357f24e7</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
         <v>24.4</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1899,15 +2238,21 @@
           <t>6a061e0355b121afe102dec7</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
         <v>223.9</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1925,15 +2270,21 @@
           <t>8165439</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
         <v>67.89</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>סלולר אדוונס אסתטיק 15/04-14/05</t>
         </is>
@@ -1955,15 +2306,21 @@
           <t>263805873</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
         <v>963.9</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>963.9</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1981,15 +2338,21 @@
           <t>263802587</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
         <v>7.35</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2007,15 +2370,21 @@
           <t>263870895</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
         <v>601.9</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>601.9</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2033,15 +2402,21 @@
           <t>806134641563</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
         <v>155.5</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2059,15 +2434,21 @@
           <t>710134822041</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
         <v>39.9</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2085,15 +2466,21 @@
           <t>2101-0099</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2111,15 +2498,21 @@
           <t>6a09fd397c3e6d96a0a4b807</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
         <v>832.6</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>832.6</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2137,15 +2530,21 @@
           <t>157807</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
         <v>8006</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>8006</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>שכירות משרד 05/26 עבור AAA</t>
         </is>
@@ -2167,15 +2566,21 @@
           <t>157808</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
         <v>3855</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>3855</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>ארנונה 05/26 עבור AAA</t>
         </is>
@@ -2197,15 +2602,21 @@
           <t>702135500397</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2223,15 +2634,21 @@
           <t>6a0aee34b2bb43469f247954</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
         <v>122.4</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2249,15 +2666,21 @@
           <t>6a0b51d676520f55718d912e</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
         <v>227.9</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2275,15 +2698,21 @@
           <t>6a0d706644cd6473ab672fa5</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2301,15 +2730,21 @@
           <t>728137003030</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2327,15 +2762,21 @@
           <t>2315-0424</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
         <v>18.82</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" s="4" t="n">
+        <v>2.9159</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2353,15 +2794,21 @@
           <t>1249-7704</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
         <v>7.8</v>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" s="4" t="n">
+        <v>2.9159</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2379,15 +2826,21 @@
           <t>6a0f0522db49a918ddf62799</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
         <v>198.9</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2405,15 +2858,21 @@
           <t>6a106fddf38386d3f4b0ec44</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
         <v>475.4</v>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>475.4</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2431,15 +2890,21 @@
           <t>1531-5377</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
         <v>15.83</v>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" s="4" t="n">
+        <v>2.8951</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2457,15 +2922,21 @@
           <t>6a117b9408f199761bd6d07b</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
         <v>190.4</v>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>190.4</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2483,15 +2954,21 @@
           <t>670138356602</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
         <v>276.6</v>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2509,15 +2986,21 @@
           <t>6a12d466b00cdda770123c65</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2535,15 +3018,21 @@
           <t>6a131d4b69fc8ce90d33354e</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2561,15 +3050,21 @@
           <t>6a13121b8557bb95a09f8d40</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
         <v>229.6</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>229.6</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2587,15 +3082,21 @@
           <t>157828</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
         <v>595</v>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>595</v>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>חשמל 18/3-18/5 עבור AAA</t>
         </is>
@@ -2617,15 +3118,21 @@
           <t>6a1478abedc073c479289c6a</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
         <v>213.8</v>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>213.8</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2643,15 +3150,21 @@
           <t>6a13db5e73fb096a324657d8</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
         <v>453.9</v>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>453.9</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2669,15 +3182,21 @@
           <t>6a145ee24f690ff23559ccb8</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
         <v>116.9</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2695,15 +3214,21 @@
           <t>6a15ea89e74d544208ed7637</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
         <v>157.9</v>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2721,15 +3246,21 @@
           <t>6a15aee5a6759269cb61d26d</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
         <v>304.2</v>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>304.2</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2747,15 +3278,21 @@
           <t>2663-4224</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="4" t="n">
+        <v>3.8026</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>334.63</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>מנוי Pro חודשי</t>
         </is>
@@ -2777,15 +3314,21 @@
           <t>2849-1904</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
         <v>239.99</v>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="4" t="n">
+        <v>2.8368</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>680.8</v>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>מנוי שנתי Plus (704.06 ש"ח)</t>
         </is>
@@ -2807,15 +3350,21 @@
           <t>6a1887f3391e950c6ce1554e</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
         <v>188.9</v>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2833,15 +3382,21 @@
           <t>6a182fe8379b1f8aff578727</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
         <v>37.25</v>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2859,15 +3414,21 @@
           <t>6a184fb82bbd834f6b19f40f</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2885,15 +3446,21 @@
           <t>6a185b01287d4a5ad7b38d8b</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2911,15 +3478,21 @@
           <t>6a188d1900d7842845f301fd</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2937,15 +3510,21 @@
           <t>2411-2135-8832</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" s="4" t="n">
+        <v>2.8068</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2963,15 +3542,21 @@
           <t>8701884</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>קבלה - גיפט קארד 300 ש"ח</t>
         </is>
@@ -2993,15 +3578,21 @@
           <t>722140557345</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
         <v>623.7</v>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>623.7</v>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>כולל מנוי Claude Max 549.90</t>
         </is>
@@ -3023,15 +3614,21 @@
           <t>6a1b0841a72b1e1a2fefc2ed</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
         <v>154.9</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3049,15 +3646,21 @@
           <t>6a1b0a98123e0b6956681400</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
         <v>356.5</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3075,15 +3678,21 @@
           <t>6a1beae81d35c54db01c86b0</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
         <v>131.5</v>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3101,15 +3710,21 @@
           <t>157949</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
         <v>3855</v>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>3855</v>
+      </c>
+      <c r="H100" t="inlineStr">
         <is>
           <t>ארנונה 06/26</t>
         </is>
@@ -3131,15 +3746,21 @@
           <t>6a1bed056dc4d0691533f9d1</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
         <v>536.9</v>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>536.9</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3157,15 +3778,21 @@
           <t>6a1d92306056e32b71a5a114</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
         <v>52.1</v>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3183,15 +3810,21 @@
           <t>6a1dbd523283645749d80871</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
         <v>285.4</v>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>285.4</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3209,15 +3842,21 @@
           <t>756003538</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
         <v>272.11</v>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>272.11</v>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>מנוי - יוסי דן גור</t>
         </is>
@@ -3239,15 +3878,21 @@
           <t>756002926</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
         <v>242.46</v>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>242.46</v>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>מנוי - אושר דן גור</t>
         </is>
@@ -3269,15 +3914,21 @@
           <t>17281413</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
         <v>43.85</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t>חשבון מאי; מס' מייל 1050416513</t>
         </is>
@@ -3299,15 +3950,21 @@
           <t>61654</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
         <v>960</v>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>לקוח: יוסף דן גור; טיפול</t>
         </is>
@@ -3329,15 +3986,21 @@
           <t>6a208270355f62bbfcf641bb</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
         <v>521.7</v>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>521.7</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3355,15 +4018,21 @@
           <t>1314450</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n">
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
         <v>2075</v>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>2075</v>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>קבלה - קייטנת קיץ (2 מחזורים + צהרון)</t>
         </is>
@@ -3385,15 +4054,21 @@
           <t>SI26019672</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n">
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
         <v>614</v>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>614</v>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t>חשבונית מרכזת לתעודת משלוח SH26006110</t>
         </is>
@@ -3415,15 +4090,21 @@
           <t>SI26019671</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
         <v>5039</v>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>5039</v>
+      </c>
+      <c r="H111" t="inlineStr">
         <is>
           <t>חשבונית מרכזת לתעודת משלוח SH26006133</t>
         </is>
@@ -3445,15 +4126,21 @@
           <t>SI26019663</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n">
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
         <v>10148</v>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>10148</v>
+      </c>
+      <c r="H112" t="inlineStr">
         <is>
           <t>חשבונית מרכזת לתעודת משלוח SH25069056</t>
         </is>
@@ -3475,15 +4162,21 @@
           <t>SI26019650</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
         <v>472</v>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>472</v>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>חשבונית מרכזת; שולם ע"י הלקוחה</t>
         </is>
@@ -3505,15 +4198,21 @@
           <t>SI26019641</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
         <v>2867</v>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>2867</v>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>חשבונית מרכזת לתעודת משלוח SH26004965</t>
         </is>
@@ -3535,15 +4234,21 @@
           <t>792142832059</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3561,15 +4266,21 @@
           <t>42854101</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" s="4" t="n">
+        <v>2.8917</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3587,15 +4298,21 @@
           <t>696143169077</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
         <v>170.3</v>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3613,15 +4330,21 @@
           <t>2587-2850</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n">
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
         <v>17.96</v>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" s="4" t="n">
+        <v>2.9116</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3639,15 +4362,21 @@
           <t>6a22c67225850a4860468054</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
         <v>328.9</v>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3665,15 +4394,21 @@
           <t>0219-0708</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n">
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
         <v>317.42</v>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>317.42</v>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>מנוי חודשי עבור אדוונס אסתטיק (OCR)</t>
         </is>
@@ -3695,15 +4430,21 @@
           <t>2271-3095-2086</t>
         </is>
       </c>
-      <c r="D121" s="2" t="n">
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" s="4" t="n">
+        <v>2.9116</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3721,15 +4462,21 @@
           <t>2038-5955-6115</t>
         </is>
       </c>
-      <c r="D122" s="2" t="n">
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" s="4" t="n">
+        <v>2.9116</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3747,15 +4494,21 @@
           <t>6a23eb0a9c59930268879dfe</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
         <v>376.32</v>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+      <c r="F123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>376.32</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3773,15 +4526,21 @@
           <t>6a2456f562b0bdcb8e96a76f</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
         <v>122.15</v>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+      <c r="F124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3799,15 +4558,21 @@
           <t>2553-5723</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n">
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
         <v>31.51</v>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" s="4" t="n">
+        <v>2.9116</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3825,15 +4590,21 @@
           <t>6a258e4c3beec3171aa6489d</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
         <v>28.4</v>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3851,15 +4622,21 @@
           <t>6a24f78c12706856bbbe62fd</t>
         </is>
       </c>
-      <c r="D127" s="2" t="n">
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
         <v>453.9</v>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>453.9</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3877,15 +4654,21 @@
           <t>SI26020048</t>
         </is>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
         <v>7080</v>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>7080</v>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>מזרקי Sculptra לאדוונס אסתטיקס</t>
         </is>
@@ -3907,15 +4690,21 @@
           <t>770145119147</t>
         </is>
       </c>
-      <c r="D129" s="2" t="n">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
         <v>153.6</v>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3933,15 +4722,21 @@
           <t>2688-4597</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n">
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
         <v>54.28</v>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" s="4" t="n">
+        <v>2.9168</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>158.32</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3959,15 +4754,21 @@
           <t>2609-1019-9091</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" s="4" t="n">
+        <v>2.9168</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3985,15 +4786,21 @@
           <t>A1117437934</t>
         </is>
       </c>
-      <c r="D132" s="2" t="n">
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
         <v>236.35</v>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>236.35</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4011,15 +4818,21 @@
           <t>6a270de63f037158b5e40f45</t>
         </is>
       </c>
-      <c r="D133" s="2" t="n">
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
         <v>86.45</v>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4037,15 +4850,21 @@
           <t>300068534487</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
         <v>264.69</v>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>264.69</v>
+      </c>
+      <c r="H134" t="inlineStr">
         <is>
           <t>קבלה לתשלום חשבונית חשמל 2026-420818154 (18/3-18/5)</t>
         </is>
@@ -4067,15 +4886,21 @@
           <t>6a2814b4d238765b51b7332f</t>
         </is>
       </c>
-      <c r="D135" s="2" t="n">
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
         <v>337.5</v>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4093,15 +4918,21 @@
           <t>2788-5628-7662</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n">
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" s="4" t="n">
+        <v>2.9784</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>134.03</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4119,15 +4950,21 @@
           <t>2751-6850-5757</t>
         </is>
       </c>
-      <c r="D137" s="2" t="n">
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" s="4" t="n">
+        <v>2.9784</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>74.45999999999999</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4145,15 +4982,21 @@
           <t>bcfb142175f38f978dbb039fe8a423ee</t>
         </is>
       </c>
-      <c r="D138" s="2" t="n">
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
         <v>6.93</v>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" s="4" t="n">
+        <v>2.9784</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4171,15 +5014,21 @@
           <t>6a292f98fe8a44aeb5c40776</t>
         </is>
       </c>
-      <c r="D139" s="2" t="n">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4197,15 +5046,21 @@
           <t>6a293a5cac2016106819d216</t>
         </is>
       </c>
-      <c r="D140" s="2" t="n">
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4223,15 +5078,21 @@
           <t>6a29608e7a3d4e1da9e8912f</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n">
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
         <v>10.2</v>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4249,15 +5110,21 @@
           <t>6a295b9948a0636c2fc9a324</t>
         </is>
       </c>
-      <c r="D142" s="2" t="n">
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
         <v>12.5</v>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4275,15 +5142,21 @@
           <t>6a2948eccd612d7150911f21</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n">
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4301,15 +5174,21 @@
           <t>35474</t>
         </is>
       </c>
-      <c r="D144" s="2" t="n">
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
         <v>569</v>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>לקוח: advance aesthetic; כיבוד קל</t>
         </is>
@@ -4331,15 +5210,21 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D145" s="2" t="n">
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
         <v>104.3</v>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="H145" t="inlineStr">
         <is>
           <t>ride receipt</t>
         </is>
@@ -4361,15 +5246,21 @@
           <t>6a2ab22c72e36e42b5cdfb1a</t>
         </is>
       </c>
-      <c r="D146" s="2" t="n">
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4387,15 +5278,21 @@
           <t>6a2ba0c423b011de091b1e41</t>
         </is>
       </c>
-      <c r="D147" s="2" t="n">
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4413,15 +5310,21 @@
           <t>6a2bd54234024d7603ecad32</t>
         </is>
       </c>
-      <c r="D148" s="2" t="n">
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
         <v>223.9</v>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4439,15 +5342,21 @@
           <t>6a2b98a923b011de091b0cb4</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
         <v>203.9</v>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4465,15 +5374,21 @@
           <t>6a2bd5efe55f3d95cfcc64e2</t>
         </is>
       </c>
-      <c r="D150" s="2" t="n">
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4491,15 +5406,21 @@
           <t>6a2d91868c2ad721784c3bf3</t>
         </is>
       </c>
-      <c r="D151" s="2" t="n">
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
         <v>436.91</v>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>436.91</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4517,15 +5438,21 @@
           <t>6a2d3a907404025164782609</t>
         </is>
       </c>
-      <c r="D152" s="2" t="n">
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
         <v>129.9</v>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4543,15 +5470,21 @@
           <t>42991799</t>
         </is>
       </c>
-      <c r="D153" s="2" t="n">
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" s="4" t="n">
+        <v>2.9207</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4569,15 +5502,21 @@
           <t>6a2e81822bb969bd56e6c02e</t>
         </is>
       </c>
-      <c r="D154" s="2" t="n">
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
         <v>7.9</v>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4595,15 +5534,21 @@
           <t>6a2e354a6499aa7d52d872c3</t>
         </is>
       </c>
-      <c r="D155" s="2" t="n">
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
         <v>473.9</v>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>473.9</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4621,15 +5566,21 @@
           <t>6a2e9c810b3647e40c7777c3</t>
         </is>
       </c>
-      <c r="D156" s="2" t="n">
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4647,15 +5598,21 @@
           <t>674147353974</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n">
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4673,15 +5630,21 @@
           <t>2241-4660</t>
         </is>
       </c>
-      <c r="D158" s="2" t="n">
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
         <v>10.05</v>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr"/>
+      <c r="F158" s="4" t="n">
+        <v>2.9113</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4699,15 +5662,21 @@
           <t>2784-5062</t>
         </is>
       </c>
-      <c r="D159" s="2" t="n">
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
         <v>45.23</v>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" s="4" t="n">
+        <v>2.9119</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>131.71</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4725,15 +5694,21 @@
           <t>6a30e6451b86e6987ef49150</t>
         </is>
       </c>
-      <c r="D160" s="2" t="n">
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
         <v>84.03</v>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4751,15 +5726,21 @@
           <t>31979</t>
         </is>
       </c>
-      <c r="D161" s="2" t="n">
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
         <v>7080</v>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>7080</v>
+      </c>
+      <c r="H161" t="inlineStr">
         <is>
           <t>לקוח: אדוונס אסתטיק אקדמי; שיעורי אקדמיה רופא עור</t>
         </is>
@@ -4781,15 +5762,21 @@
           <t>157956</t>
         </is>
       </c>
-      <c r="D162" s="2" t="n">
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
         <v>8006</v>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
+      <c r="F162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>8006</v>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t>שכירות משרד 06/26 - חיוב כפול שבוטל בזיכוי 8931</t>
         </is>
@@ -4811,15 +5798,21 @@
           <t>8931</t>
         </is>
       </c>
-      <c r="D163" s="2" t="n">
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
         <v>-8006</v>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>-8006</v>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>חשבונית זיכוי כנגד 157956</t>
         </is>
@@ -4841,15 +5834,21 @@
           <t>157958</t>
         </is>
       </c>
-      <c r="D164" s="2" t="n">
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
         <v>8006</v>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>8006</v>
+      </c>
+      <c r="H164" t="inlineStr">
         <is>
           <t>שכירות משרד 06/26 עבור AAA</t>
         </is>
@@ -4871,15 +5870,21 @@
           <t>2085-3497</t>
         </is>
       </c>
-      <c r="D165" s="2" t="n">
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4897,15 +5902,21 @@
           <t>4fa8491b-079f-4571-b20c-03c1b4b3262a</t>
         </is>
       </c>
-      <c r="D166" s="2" t="n">
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
         <v>49.95</v>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" s="4" t="n">
+        <v>2.9207</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>145.89</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4923,15 +5934,21 @@
           <t>6a324b36712505e98a2410dd</t>
         </is>
       </c>
-      <c r="D167" s="2" t="n">
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
         <v>7.35</v>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4949,15 +5966,21 @@
           <t>6a32a7d48b1a96055286fc52</t>
         </is>
       </c>
-      <c r="D168" s="2" t="n">
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4975,15 +5998,21 @@
           <t>35532</t>
         </is>
       </c>
-      <c r="D169" s="2" t="n">
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
         <v>549</v>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
+      <c r="F169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>549</v>
+      </c>
+      <c r="H169" t="inlineStr">
         <is>
           <t>לקוח: advance aesthetic; כיבוד קל</t>
         </is>
@@ -5005,15 +6034,21 @@
           <t>676149133825</t>
         </is>
       </c>
-      <c r="D170" s="2" t="n">
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
         <v>189.5</v>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5031,15 +6066,21 @@
           <t>772148842582</t>
         </is>
       </c>
-      <c r="D171" s="2" t="n">
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
         <v>39.9</v>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5057,15 +6098,21 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D172" s="2" t="n">
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
         <v>128.8</v>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
+      <c r="F172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="H172" t="inlineStr">
         <is>
           <t>ride receipt</t>
         </is>
@@ -5087,15 +6134,21 @@
           <t>6a33d0252dc79de16dcdb285</t>
         </is>
       </c>
-      <c r="D173" s="2" t="n">
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5113,15 +6166,21 @@
           <t>6a33e40df471df0a91e5365e</t>
         </is>
       </c>
-      <c r="D174" s="2" t="n">
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5139,15 +6198,21 @@
           <t>91</t>
         </is>
       </c>
-      <c r="D175" s="2" t="n">
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
         <v>1416</v>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
+      <c r="F175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="H175" t="inlineStr">
         <is>
           <t>לקוח: יוסף דן גור ואדוונס אסתטיק; צילום ועריכת וידאו</t>
         </is>
@@ -5169,15 +6234,21 @@
           <t>98013</t>
         </is>
       </c>
-      <c r="D176" s="2" t="n">
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
+      <c r="F176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H176" t="inlineStr">
         <is>
           <t>לקוח: אושר דנגור; קבלה 66875</t>
         </is>
@@ -5199,15 +6270,21 @@
           <t>766149407181</t>
         </is>
       </c>
-      <c r="D177" s="2" t="n">
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5225,15 +6302,21 @@
           <t>6a34e1bd74c1c0cad082fa94</t>
         </is>
       </c>
-      <c r="D178" s="2" t="n">
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
         <v>176.8</v>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5251,15 +6334,21 @@
           <t>2190-5575</t>
         </is>
       </c>
-      <c r="D179" s="2" t="n">
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
         <v>55.85</v>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" s="4" t="n">
+        <v>2.9622</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>165.44</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5277,15 +6366,21 @@
           <t>6a36d46121879575d4edd147</t>
         </is>
       </c>
-      <c r="D180" s="2" t="n">
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
         <v>397.9</v>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5303,15 +6398,21 @@
           <t>6a37a5c861c0c95bb6ee0c3a</t>
         </is>
       </c>
-      <c r="D181" s="2" t="n">
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
         <v>75.15000000000001</v>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5329,15 +6430,21 @@
           <t>6a37c523a0a6142bfedef0e8</t>
         </is>
       </c>
-      <c r="D182" s="2" t="n">
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
         <v>9.9</v>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5355,15 +6462,21 @@
           <t>6a37ea44b89e0b04dae58de2</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5381,15 +6494,21 @@
           <t>6a37fc5cccd8f1c7cc6c0aa5</t>
         </is>
       </c>
-      <c r="D184" s="2" t="n">
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr"/>
+      <c r="F184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5407,15 +6526,21 @@
           <t>6a39683a66035c0c6f96d39d</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n">
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
         <v>151.9</v>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5433,15 +6558,21 @@
           <t>6a394f0d451b654767818a14</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n">
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
         <v>83.5</v>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5459,15 +6590,21 @@
           <t>6a39105a0ef82670f7ec6d5d</t>
         </is>
       </c>
-      <c r="D187" s="2" t="n">
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
         <v>187.9</v>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5485,15 +6622,21 @@
           <t>6a396b22016402541fe8e69b</t>
         </is>
       </c>
-      <c r="D188" s="2" t="n">
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
         <v>67.41</v>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
+      <c r="F188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>67.41</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5511,15 +6654,21 @@
           <t>860151209430</t>
         </is>
       </c>
-      <c r="D189" s="2" t="n">
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
         <v>111.7</v>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5537,15 +6686,21 @@
           <t>6a3a8d239ef75da7206742a3</t>
         </is>
       </c>
-      <c r="D190" s="2" t="n">
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
         <v>155.9</v>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5563,15 +6718,21 @@
           <t>6a3a8bcd248e79fff4c85210</t>
         </is>
       </c>
-      <c r="D191" s="2" t="n">
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
         <v>242.3</v>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
+      <c r="F191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>242.3</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5589,15 +6750,21 @@
           <t>6a3a17027cf8518cb7655d7d</t>
         </is>
       </c>
-      <c r="D192" s="2" t="n">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
         <v>147.1</v>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
+      <c r="F192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>147.1</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5615,15 +6782,21 @@
           <t>6a3bb31c20ed8c2b39863eb3</t>
         </is>
       </c>
-      <c r="D193" s="2" t="n">
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5641,15 +6814,21 @@
           <t>6a3c135607d63582ab4cf1ca</t>
         </is>
       </c>
-      <c r="D194" s="2" t="n">
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
         <v>5.9</v>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
+      <c r="F194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5667,15 +6846,21 @@
           <t>6a3bac9e28d256eac4e2bedb</t>
         </is>
       </c>
-      <c r="D195" s="2" t="n">
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
         <v>101.05</v>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
+      <c r="F195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5693,15 +6878,21 @@
           <t>35617</t>
         </is>
       </c>
-      <c r="D196" s="2" t="n">
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
         <v>554</v>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
+      <c r="F196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="H196" t="inlineStr">
         <is>
           <t>לקוח: advance aesthetic; כיבוד קל</t>
         </is>
@@ -5723,15 +6914,21 @@
           <t>660152079688</t>
         </is>
       </c>
-      <c r="D197" s="2" t="n">
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
         <v>204.7</v>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5749,15 +6946,21 @@
           <t>2032-1302</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n">
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
         <v>29.9</v>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" s="4" t="n">
+        <v>2.9759</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5775,15 +6978,21 @@
           <t>6a3cd1892144f56a723baee3</t>
         </is>
       </c>
-      <c r="D199" s="2" t="n">
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
         <v>215.3</v>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
+      <c r="F199" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5801,15 +7010,21 @@
           <t>6a3d39dbd04a9ba7012e76f6</t>
         </is>
       </c>
-      <c r="D200" s="2" t="n">
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
         <v>99.58</v>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5827,15 +7042,21 @@
           <t>6a3cd0491a52d881e10d368a</t>
         </is>
       </c>
-      <c r="D201" s="2" t="n">
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
         <v>102.1</v>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr"/>
+      <c r="F201" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5853,15 +7074,21 @@
           <t>2100-7812-2329</t>
         </is>
       </c>
-      <c r="D202" s="2" t="n">
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr"/>
+      <c r="F202" s="4" t="n">
+        <v>2.9979</v>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5879,15 +7106,21 @@
           <t>2636-0541</t>
         </is>
       </c>
-      <c r="D203" s="2" t="n">
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr"/>
+      <c r="F203" s="4" t="n">
+        <v>3.9626</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>348.71</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5905,15 +7138,21 @@
           <t>6a40cc99dd87f246e4ccc825</t>
         </is>
       </c>
-      <c r="D204" s="2" t="n">
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr"/>
+      <c r="F204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5931,15 +7170,21 @@
           <t>6a40df63eff9c2ec1542c73f</t>
         </is>
       </c>
-      <c r="D205" s="2" t="n">
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
+      <c r="F205" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5957,15 +7202,21 @@
           <t>6a40fb6a8a8cd780d12e0f94</t>
         </is>
       </c>
-      <c r="D206" s="2" t="n">
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5983,15 +7234,21 @@
           <t>6a4103061f10220f73e4c429</t>
         </is>
       </c>
-      <c r="D207" s="2" t="n">
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
         <v>41.3</v>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
+      <c r="F207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6009,15 +7266,21 @@
           <t>6a40ae9c32dd0cbd35c0a5c0</t>
         </is>
       </c>
-      <c r="D208" s="2" t="n">
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
         <v>453.9</v>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
+      <c r="F208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>453.9</v>
+      </c>
+      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6035,15 +7298,21 @@
           <t>61707</t>
         </is>
       </c>
-      <c r="D209" s="2" t="n">
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
         <v>960</v>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
+      <c r="F209" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="H209" t="inlineStr">
         <is>
           <t>לקוח: יוסף דן גור; טיפול</t>
         </is>
@@ -6065,15 +7334,21 @@
           <t>850154719044</t>
         </is>
       </c>
-      <c r="D210" s="2" t="n">
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
         <v>519.6</v>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr"/>
+      <c r="F210" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>519.6</v>
+      </c>
+      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6091,15 +7366,21 @@
           <t>5612919402</t>
         </is>
       </c>
-      <c r="D211" s="2" t="n">
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
         <v>2.72</v>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
+      <c r="F211" s="4" t="n">
+        <v>3.3953</v>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="H211" t="inlineStr">
         <is>
           <t>Business Starter 19-30.6</t>
         </is>
@@ -6121,15 +7402,21 @@
           <t>6a43d06bbc575909ea076559</t>
         </is>
       </c>
-      <c r="D212" s="2" t="n">
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
         <v>161.9</v>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6147,15 +7434,21 @@
           <t>6a438ce43d4cfa2f31d8aacf</t>
         </is>
       </c>
-      <c r="D213" s="2" t="n">
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6173,15 +7466,21 @@
           <t>6a438c9bbfc6821a66b779ec</t>
         </is>
       </c>
-      <c r="D214" s="2" t="n">
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
         <v>186.9</v>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
+      <c r="F214" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6199,15 +7498,21 @@
           <t>158110</t>
         </is>
       </c>
-      <c r="D215" s="2" t="n">
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
         <v>7830</v>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
+      <c r="F215" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>7830</v>
+      </c>
+      <c r="H215" t="inlineStr">
         <is>
           <t>ארנונה 7-8/26 עבור AAA</t>
         </is>
@@ -6229,15 +7534,21 @@
           <t>186881</t>
         </is>
       </c>
-      <c r="D216" s="2" t="n">
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
         <v>424.61</v>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
+      <c r="F216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>424.61</v>
+      </c>
+      <c r="H216" t="inlineStr">
         <is>
           <t>עמלות סליקה יוני; מחזור 26430 הועבר נטו 26005.39</t>
         </is>
@@ -6259,15 +7570,21 @@
           <t>01/010057</t>
         </is>
       </c>
-      <c r="D217" s="2" t="n">
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
         <v>3245</v>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
+      <c r="F217" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>3245</v>
+      </c>
+      <c r="H217" t="inlineStr">
         <is>
           <t>שכירות 06/26 חלק 1 מתוך 2</t>
         </is>
@@ -6289,67 +7606,68 @@
           <t>01/010058</t>
         </is>
       </c>
-      <c r="D218" s="2" t="n">
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
         <v>3245</v>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
+      <c r="F218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="2" t="n">
+        <v>3245</v>
+      </c>
+      <c r="H218" t="inlineStr">
         <is>
           <t>שכירות 06/26 חלק 2 מתוך 2</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>סה"כ</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="n">
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ בש"ח</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="n">
+        <v>117641.95</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>מזה במקור EUR</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
         <v>2.72</v>
       </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="D221" s="4" t="n">
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>מזה במקור GBP</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
         <v>176</v>
       </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="D222" s="4" t="n">
-        <v>114419.04</v>
-      </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
     </row>
     <row r="223">
-      <c r="D223" s="4" t="n">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>מזה במקור USD</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
         <v>872.1</v>
       </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
     </row>
     <row r="225">
-      <c r="A225" s="5" t="inlineStr">
+      <c r="A225" s="7" t="inlineStr">
         <is>
           <t>מסמכים ללא סכום (הקובץ לא היה נגיש) - מספרי החשבונית ידועים</t>
         </is>
@@ -6371,7 +7689,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="H226" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן</t>
         </is>
@@ -6393,7 +7711,7 @@
           <t>RC269170767</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="H227" t="inlineStr">
         <is>
           <t>קבלה/חשבונית מצורפת - לא סונכרנה</t>
         </is>
@@ -6415,7 +7733,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>חשבונית מצורפת - לא סונכרנה</t>
         </is>
@@ -6437,7 +7755,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="H229" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן</t>
         </is>
@@ -6459,7 +7777,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>אישור רישום לפעילות - קבלה לא סונכרנה</t>
         </is>
@@ -6481,7 +7799,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="H231" t="inlineStr">
         <is>
           <t>הודעה - החשבונית באתר</t>
         </is>
@@ -6503,7 +7821,7 @@
           <t>184818</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="H232" t="inlineStr">
         <is>
           <t>קבלה בקובץ מצורף - לא נגיש</t>
         </is>
@@ -6525,7 +7843,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="H233" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן</t>
         </is>
@@ -6547,7 +7865,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="H234" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן</t>
         </is>
@@ -6569,7 +7887,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="H235" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן</t>
         </is>
@@ -6591,7 +7909,7 @@
           <t>זיכוי-1009326346</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="H236" t="inlineStr">
         <is>
           <t>זיכוי ביטול חשבונית 1009326346</t>
         </is>
@@ -6613,7 +7931,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
+      <c r="H237" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן</t>
         </is>
@@ -6635,7 +7953,7 @@
           <t>1009513336</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
+      <c r="H238" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן - octet-stream</t>
         </is>
@@ -6657,7 +7975,7 @@
           <t>1009535688</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="H239" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן - octet-stream</t>
         </is>
@@ -6679,7 +7997,7 @@
           <t>1009589130</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
+      <c r="H240" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן - octet-stream</t>
         </is>
@@ -6701,7 +8019,7 @@
           <t>1009636310</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
+      <c r="H241" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן - octet-stream</t>
         </is>
@@ -6723,7 +8041,7 @@
           <t>1009647719</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="H242" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן - octet-stream</t>
         </is>
@@ -6745,7 +8063,7 @@
           <t>1009703108</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="H243" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן - octet-stream</t>
         </is>
@@ -6767,9 +8085,16 @@
           <t>1009776913</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
+      <c r="H244" t="inlineStr">
         <is>
           <t>קובץ לא סונכרן - octet-stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>המרות מט"ח לפי שער יציג יומי (ECB/Frankfurter) ליום המסמך; בסופ"ש - יום העסקים הקודם</t>
         </is>
       </c>
     </row>

--- a/invoices/exports/expenses-2026-05-06.xlsx
+++ b/invoices/exports/expenses-2026-05-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הוצאות מאי-יוני 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="סטטוס" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="הוצאות מאי-יוני 2026" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,18 @@
     <font>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F7A33"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45F06"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -78,6 +91,9 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,6 +459,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>סטטוס מערכת איסוף החשבוניות — נכון ל-13.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>רכיב</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>מצב</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>איסוף מהמייל (osherv55@gmail.com), מאי-יוני 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>הושלם — 285 מסמכים בטבלה המרכזית</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>דוח הוצאות לרו"ח (גיליון "הוצאות מאי-יוני 2026")</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>מוכן — 236 מסמכי הוצאה, 217 עם סכום מלא</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>סה"כ הוצאות בש"ח (כולל המרות מט"ח לפי שער יומי)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>117,641.95 ₪</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>הכנסות שזוהו (לא בדוח זה)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>39,550 ₪ — קורס + מסוף אשראי</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>סנכרון יומי אוטומטי מייל→דרייב (6:00)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>בדיקה והשלמה אוטומטית שלי (4 פעמים ביום)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>פעילה</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>בהשלמה אוטומטית בימים הקרובים</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4 קבלות מתחילת מאי (פתאל, סופר-פארם, אייס, קייטנה)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>ממתין לריצת הסנכרון הבאה</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14 חיובי רבו פילאטיס (הוצאה אישית, כנראה לא רלוונטי לרו"ח)</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>דורש הרצת גרסה 4 של הסקריפט</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>חשבונית צמרת מימונים</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>זמינה רק בהתחברות לאתר שלהם — ידני</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -528,7 +705,6 @@
       <c r="G2" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +736,6 @@
       <c r="G3" s="2" t="n">
         <v>155.93</v>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -592,7 +767,6 @@
       <c r="G4" s="2" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -624,7 +798,6 @@
       <c r="G5" s="2" t="n">
         <v>268.9</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -656,7 +829,6 @@
       <c r="G6" s="2" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -688,7 +860,6 @@
       <c r="G7" s="2" t="n">
         <v>201.2</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -720,7 +891,6 @@
       <c r="G8" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -752,7 +922,6 @@
       <c r="G9" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -892,7 +1061,6 @@
       <c r="G13" s="2" t="n">
         <v>57.25</v>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -924,7 +1092,6 @@
       <c r="G14" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -956,7 +1123,6 @@
       <c r="G15" s="2" t="n">
         <v>137.6</v>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -988,7 +1154,6 @@
       <c r="G16" s="2" t="n">
         <v>134.3</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1020,7 +1185,6 @@
       <c r="G17" s="2" t="n">
         <v>128.35</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1088,7 +1252,6 @@
       <c r="G19" s="2" t="n">
         <v>135.6</v>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1156,7 +1319,6 @@
       <c r="G21" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1188,7 +1350,6 @@
       <c r="G22" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1220,7 +1381,6 @@
       <c r="G23" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1252,7 +1412,6 @@
       <c r="G24" s="2" t="n">
         <v>332.9</v>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1284,7 +1443,6 @@
       <c r="G25" s="2" t="n">
         <v>200.88</v>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1388,7 +1546,6 @@
       <c r="G28" s="2" t="n">
         <v>119.45</v>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1420,7 +1577,6 @@
       <c r="G29" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1452,7 +1608,6 @@
       <c r="G30" s="2" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1484,7 +1639,6 @@
       <c r="G31" s="2" t="n">
         <v>427.9</v>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1516,7 +1670,6 @@
       <c r="G32" s="2" t="n">
         <v>63.91</v>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1548,7 +1701,6 @@
       <c r="G33" s="2" t="n">
         <v>493.9</v>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1580,7 +1732,6 @@
       <c r="G34" s="2" t="n">
         <v>171.9</v>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1612,7 +1763,6 @@
       <c r="G35" s="2" t="n">
         <v>29.25</v>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1644,7 +1794,6 @@
       <c r="G36" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1676,7 +1825,6 @@
       <c r="G37" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1708,7 +1856,6 @@
       <c r="G38" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1740,7 +1887,6 @@
       <c r="G39" s="2" t="n">
         <v>214.9</v>
       </c>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1772,7 +1918,6 @@
       <c r="G40" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1804,7 +1949,6 @@
       <c r="G41" s="2" t="n">
         <v>88.2</v>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1836,7 +1980,6 @@
       <c r="G42" s="2" t="n">
         <v>333.9</v>
       </c>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1868,7 +2011,6 @@
       <c r="G43" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1900,7 +2042,6 @@
       <c r="G44" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1932,7 +2073,6 @@
       <c r="G45" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1964,7 +2104,6 @@
       <c r="G46" s="2" t="n">
         <v>58.16</v>
       </c>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1996,7 +2135,6 @@
       <c r="G47" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2028,7 +2166,6 @@
       <c r="G48" s="2" t="n">
         <v>199.9</v>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2060,7 +2197,6 @@
       <c r="G49" s="2" t="n">
         <v>318.94</v>
       </c>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2092,7 +2228,6 @@
       <c r="G50" s="2" t="n">
         <v>130.74</v>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2124,7 +2259,6 @@
       <c r="G51" s="2" t="n">
         <v>636.9</v>
       </c>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2156,7 +2290,6 @@
       <c r="G52" s="2" t="n">
         <v>25.05</v>
       </c>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2188,7 +2321,6 @@
       <c r="G53" s="2" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2220,7 +2352,6 @@
       <c r="G54" s="2" t="n">
         <v>24.4</v>
       </c>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2252,7 +2383,6 @@
       <c r="G55" s="2" t="n">
         <v>223.9</v>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2320,7 +2450,6 @@
       <c r="G57" s="2" t="n">
         <v>963.9</v>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2352,7 +2481,6 @@
       <c r="G58" s="2" t="n">
         <v>7.35</v>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2384,7 +2512,6 @@
       <c r="G59" s="2" t="n">
         <v>601.9</v>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2416,7 +2543,6 @@
       <c r="G60" s="2" t="n">
         <v>155.5</v>
       </c>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2448,7 +2574,6 @@
       <c r="G61" s="2" t="n">
         <v>39.9</v>
       </c>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2480,7 +2605,6 @@
       <c r="G62" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2512,7 +2636,6 @@
       <c r="G63" s="2" t="n">
         <v>832.6</v>
       </c>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2616,7 +2739,6 @@
       <c r="G66" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2648,7 +2770,6 @@
       <c r="G67" s="2" t="n">
         <v>122.4</v>
       </c>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2680,7 +2801,6 @@
       <c r="G68" s="2" t="n">
         <v>227.9</v>
       </c>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2712,7 +2832,6 @@
       <c r="G69" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2744,7 +2863,6 @@
       <c r="G70" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2776,7 +2894,6 @@
       <c r="G71" s="2" t="n">
         <v>54.88</v>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2808,7 +2925,6 @@
       <c r="G72" s="2" t="n">
         <v>22.74</v>
       </c>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2840,7 +2956,6 @@
       <c r="G73" s="2" t="n">
         <v>198.9</v>
       </c>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2872,7 +2987,6 @@
       <c r="G74" s="2" t="n">
         <v>475.4</v>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2904,7 +3018,6 @@
       <c r="G75" s="2" t="n">
         <v>45.83</v>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2936,7 +3049,6 @@
       <c r="G76" s="2" t="n">
         <v>190.4</v>
       </c>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2968,7 +3080,6 @@
       <c r="G77" s="2" t="n">
         <v>276.6</v>
       </c>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3000,7 +3111,6 @@
       <c r="G78" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3032,7 +3142,6 @@
       <c r="G79" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3064,7 +3173,6 @@
       <c r="G80" s="2" t="n">
         <v>229.6</v>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3132,7 +3240,6 @@
       <c r="G82" s="2" t="n">
         <v>213.8</v>
       </c>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3164,7 +3271,6 @@
       <c r="G83" s="2" t="n">
         <v>453.9</v>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3196,7 +3302,6 @@
       <c r="G84" s="2" t="n">
         <v>116.9</v>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3228,7 +3333,6 @@
       <c r="G85" s="2" t="n">
         <v>157.9</v>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3260,7 +3364,6 @@
       <c r="G86" s="2" t="n">
         <v>304.2</v>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3364,7 +3467,6 @@
       <c r="G89" s="2" t="n">
         <v>188.9</v>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3396,7 +3498,6 @@
       <c r="G90" s="2" t="n">
         <v>37.25</v>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3428,7 +3529,6 @@
       <c r="G91" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3460,7 +3560,6 @@
       <c r="G92" s="2" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3492,7 +3591,6 @@
       <c r="G93" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3524,7 +3622,6 @@
       <c r="G94" s="2" t="n">
         <v>70.17</v>
       </c>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3628,7 +3725,6 @@
       <c r="G97" s="2" t="n">
         <v>154.9</v>
       </c>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3660,7 +3756,6 @@
       <c r="G98" s="2" t="n">
         <v>356.5</v>
       </c>
-      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3692,7 +3787,6 @@
       <c r="G99" s="2" t="n">
         <v>131.5</v>
       </c>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3760,7 +3854,6 @@
       <c r="G101" s="2" t="n">
         <v>536.9</v>
       </c>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3792,7 +3885,6 @@
       <c r="G102" s="2" t="n">
         <v>52.1</v>
       </c>
-      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3824,7 +3916,6 @@
       <c r="G103" s="2" t="n">
         <v>285.4</v>
       </c>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4000,7 +4091,6 @@
       <c r="G108" s="2" t="n">
         <v>521.7</v>
       </c>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4248,7 +4338,6 @@
       <c r="G115" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4280,7 +4369,6 @@
       <c r="G116" s="2" t="n">
         <v>34.7</v>
       </c>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4312,7 +4400,6 @@
       <c r="G117" s="2" t="n">
         <v>170.3</v>
       </c>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4344,7 +4431,6 @@
       <c r="G118" s="2" t="n">
         <v>52.29</v>
       </c>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4376,7 +4462,6 @@
       <c r="G119" s="2" t="n">
         <v>328.9</v>
       </c>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4444,7 +4529,6 @@
       <c r="G121" s="2" t="n">
         <v>58.23</v>
       </c>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4476,7 +4560,6 @@
       <c r="G122" s="2" t="n">
         <v>58.23</v>
       </c>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4508,7 +4591,6 @@
       <c r="G123" s="2" t="n">
         <v>376.32</v>
       </c>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4540,7 +4622,6 @@
       <c r="G124" s="2" t="n">
         <v>122.15</v>
       </c>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4572,7 +4653,6 @@
       <c r="G125" s="2" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4604,7 +4684,6 @@
       <c r="G126" s="2" t="n">
         <v>28.4</v>
       </c>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4636,7 +4715,6 @@
       <c r="G127" s="2" t="n">
         <v>453.9</v>
       </c>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4704,7 +4782,6 @@
       <c r="G129" s="2" t="n">
         <v>153.6</v>
       </c>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4736,7 +4813,6 @@
       <c r="G130" s="2" t="n">
         <v>158.32</v>
       </c>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4768,7 +4844,6 @@
       <c r="G131" s="2" t="n">
         <v>64.17</v>
       </c>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4800,7 +4875,6 @@
       <c r="G132" s="2" t="n">
         <v>236.35</v>
       </c>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4832,7 +4906,6 @@
       <c r="G133" s="2" t="n">
         <v>86.45</v>
       </c>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4900,7 +4973,6 @@
       <c r="G135" s="2" t="n">
         <v>337.5</v>
       </c>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4932,7 +5004,6 @@
       <c r="G136" s="2" t="n">
         <v>134.03</v>
       </c>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4964,7 +5035,6 @@
       <c r="G137" s="2" t="n">
         <v>74.45999999999999</v>
       </c>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4996,7 +5066,6 @@
       <c r="G138" s="2" t="n">
         <v>20.64</v>
       </c>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5028,7 +5097,6 @@
       <c r="G139" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5060,7 +5128,6 @@
       <c r="G140" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5092,7 +5159,6 @@
       <c r="G141" s="2" t="n">
         <v>10.2</v>
       </c>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5124,7 +5190,6 @@
       <c r="G142" s="2" t="n">
         <v>12.5</v>
       </c>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5156,7 +5221,6 @@
       <c r="G143" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5260,7 +5324,6 @@
       <c r="G146" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5292,7 +5355,6 @@
       <c r="G147" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5324,7 +5386,6 @@
       <c r="G148" s="2" t="n">
         <v>223.9</v>
       </c>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5356,7 +5417,6 @@
       <c r="G149" s="2" t="n">
         <v>203.9</v>
       </c>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5388,7 +5448,6 @@
       <c r="G150" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5420,7 +5479,6 @@
       <c r="G151" s="2" t="n">
         <v>436.91</v>
       </c>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5452,7 +5510,6 @@
       <c r="G152" s="2" t="n">
         <v>129.9</v>
       </c>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5484,7 +5541,6 @@
       <c r="G153" s="2" t="n">
         <v>35.05</v>
       </c>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5516,7 +5572,6 @@
       <c r="G154" s="2" t="n">
         <v>7.9</v>
       </c>
-      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5548,7 +5603,6 @@
       <c r="G155" s="2" t="n">
         <v>473.9</v>
       </c>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5580,7 +5634,6 @@
       <c r="G156" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5612,7 +5665,6 @@
       <c r="G157" s="2" t="n">
         <v>13.9</v>
       </c>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5644,7 +5696,6 @@
       <c r="G158" s="2" t="n">
         <v>29.26</v>
       </c>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5676,7 +5727,6 @@
       <c r="G159" s="2" t="n">
         <v>131.71</v>
       </c>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5708,7 +5758,6 @@
       <c r="G160" s="2" t="n">
         <v>84.03</v>
       </c>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5884,7 +5933,6 @@
       <c r="G165" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5916,7 +5964,6 @@
       <c r="G166" s="2" t="n">
         <v>145.89</v>
       </c>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5948,7 +5995,6 @@
       <c r="G167" s="2" t="n">
         <v>7.35</v>
       </c>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5980,7 +6026,6 @@
       <c r="G168" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6048,7 +6093,6 @@
       <c r="G170" s="2" t="n">
         <v>189.5</v>
       </c>
-      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6080,7 +6124,6 @@
       <c r="G171" s="2" t="n">
         <v>39.9</v>
       </c>
-      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6148,7 +6191,6 @@
       <c r="G173" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6180,7 +6222,6 @@
       <c r="G174" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6284,7 +6325,6 @@
       <c r="G177" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6316,7 +6356,6 @@
       <c r="G178" s="2" t="n">
         <v>176.8</v>
       </c>
-      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6348,7 +6387,6 @@
       <c r="G179" s="2" t="n">
         <v>165.44</v>
       </c>
-      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6380,7 +6418,6 @@
       <c r="G180" s="2" t="n">
         <v>397.9</v>
       </c>
-      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6412,7 +6449,6 @@
       <c r="G181" s="2" t="n">
         <v>75.15000000000001</v>
       </c>
-      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6444,7 +6480,6 @@
       <c r="G182" s="2" t="n">
         <v>9.9</v>
       </c>
-      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6476,7 +6511,6 @@
       <c r="G183" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6508,7 +6542,6 @@
       <c r="G184" s="2" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6540,7 +6573,6 @@
       <c r="G185" s="2" t="n">
         <v>151.9</v>
       </c>
-      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6572,7 +6604,6 @@
       <c r="G186" s="2" t="n">
         <v>83.5</v>
       </c>
-      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6604,7 +6635,6 @@
       <c r="G187" s="2" t="n">
         <v>187.9</v>
       </c>
-      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6636,7 +6666,6 @@
       <c r="G188" s="2" t="n">
         <v>67.41</v>
       </c>
-      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6668,7 +6697,6 @@
       <c r="G189" s="2" t="n">
         <v>111.7</v>
       </c>
-      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6700,7 +6728,6 @@
       <c r="G190" s="2" t="n">
         <v>155.9</v>
       </c>
-      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6732,7 +6759,6 @@
       <c r="G191" s="2" t="n">
         <v>242.3</v>
       </c>
-      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6764,7 +6790,6 @@
       <c r="G192" s="2" t="n">
         <v>147.1</v>
       </c>
-      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6796,7 +6821,6 @@
       <c r="G193" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6828,7 +6852,6 @@
       <c r="G194" s="2" t="n">
         <v>5.9</v>
       </c>
-      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6860,7 +6883,6 @@
       <c r="G195" s="2" t="n">
         <v>101.05</v>
       </c>
-      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6928,7 +6950,6 @@
       <c r="G197" s="2" t="n">
         <v>204.7</v>
       </c>
-      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6960,7 +6981,6 @@
       <c r="G198" s="2" t="n">
         <v>88.98</v>
       </c>
-      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6992,7 +7012,6 @@
       <c r="G199" s="2" t="n">
         <v>215.3</v>
       </c>
-      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7024,7 +7043,6 @@
       <c r="G200" s="2" t="n">
         <v>99.58</v>
       </c>
-      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7056,7 +7074,6 @@
       <c r="G201" s="2" t="n">
         <v>102.1</v>
       </c>
-      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7088,7 +7105,6 @@
       <c r="G202" s="2" t="n">
         <v>59.96</v>
       </c>
-      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7120,7 +7136,6 @@
       <c r="G203" s="2" t="n">
         <v>348.71</v>
       </c>
-      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7152,7 +7167,6 @@
       <c r="G204" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7184,7 +7198,6 @@
       <c r="G205" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7216,7 +7229,6 @@
       <c r="G206" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7248,7 +7260,6 @@
       <c r="G207" s="2" t="n">
         <v>41.3</v>
       </c>
-      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7280,7 +7291,6 @@
       <c r="G208" s="2" t="n">
         <v>453.9</v>
       </c>
-      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7348,7 +7358,6 @@
       <c r="G210" s="2" t="n">
         <v>519.6</v>
       </c>
-      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7416,7 +7425,6 @@
       <c r="G212" s="2" t="n">
         <v>161.9</v>
       </c>
-      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7448,7 +7456,6 @@
       <c r="G213" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7480,7 +7487,6 @@
       <c r="G214" s="2" t="n">
         <v>186.9</v>
       </c>
-      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
